--- a/Fanincial Account/Onelick.xlsx
+++ b/Fanincial Account/Onelick.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
-    <sheet name="one" sheetId="1" r:id="rId1"/>
+    <sheet name="one Stytem" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Invontory" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="86">
   <si>
     <t>No:</t>
   </si>
@@ -279,121 +278,16 @@
   </si>
   <si>
     <t xml:space="preserve"> Revenue</t>
-  </si>
-  <si>
-    <t>Image</t>
-  </si>
-  <si>
-    <t>Products Name</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Total  Cost</t>
-  </si>
-  <si>
-    <t>Samsung Galxy 26 Ultuy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Koria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit  - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty </t>
-  </si>
-  <si>
-    <t>Samsung Galxy 25 Ultuy</t>
-  </si>
-  <si>
-    <t>Chine</t>
-  </si>
-  <si>
-    <t>I Phone 17pro</t>
-  </si>
-  <si>
-    <t>Tecno W5</t>
-  </si>
-  <si>
-    <t>Thailand</t>
-  </si>
-  <si>
-    <t>Box Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Store Balance </t>
-  </si>
-  <si>
-    <t>Invontory  Store</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Invontory  purchases</t>
-  </si>
-  <si>
-    <t>General Journal</t>
-  </si>
-  <si>
-    <t>Page</t>
-  </si>
-  <si>
-    <t>Ref…</t>
-  </si>
-  <si>
-    <t>Account Titles and Exlanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Owner's Equits</t>
-  </si>
-  <si>
-    <t>Balance Sheet</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Liabilities And Owner's Equits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        Total Liabilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Owner's Equits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       Total  Owner's Equits</t>
-  </si>
-  <si>
-    <t>Total  Liabilities And Owner's Equits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Total Assets</t>
-  </si>
-  <si>
-    <t>I Phone 15pro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,24 +408,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,14 +440,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="29">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -864,50 +736,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1078,25 +912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1163,51 +978,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1488,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:BX109"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -1551,98 +1323,98 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:74" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="S2" s="101" t="s">
+      <c r="S2" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="T2" s="101"/>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
-      <c r="Y2" s="101"/>
-      <c r="Z2" s="101"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="101"/>
-      <c r="AD2" s="101"/>
-      <c r="AE2" s="101"/>
-      <c r="AF2" s="101"/>
-      <c r="AG2" s="101"/>
-      <c r="AH2" s="101"/>
-      <c r="AI2" s="101"/>
-      <c r="AJ2" s="101"/>
-      <c r="AK2" s="101"/>
-      <c r="AL2" s="101"/>
-      <c r="AM2" s="101"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="88"/>
+      <c r="Y2" s="88"/>
+      <c r="Z2" s="88"/>
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="88"/>
+      <c r="AC2" s="88"/>
+      <c r="AD2" s="88"/>
+      <c r="AE2" s="88"/>
+      <c r="AF2" s="88"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="88"/>
+      <c r="AI2" s="88"/>
+      <c r="AJ2" s="88"/>
+      <c r="AK2" s="88"/>
+      <c r="AL2" s="88"/>
+      <c r="AM2" s="88"/>
       <c r="AN2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="AO2" s="101" t="s">
+      <c r="AO2" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="AP2" s="101"/>
-      <c r="AQ2" s="101"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="101"/>
-      <c r="AT2" s="101"/>
+      <c r="AP2" s="88"/>
+      <c r="AQ2" s="88"/>
+      <c r="AR2" s="88"/>
+      <c r="AS2" s="88"/>
+      <c r="AT2" s="88"/>
       <c r="AU2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="AV2" s="101" t="s">
+      <c r="AV2" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="AW2" s="101"/>
-      <c r="AX2" s="101"/>
-      <c r="AY2" s="101"/>
-      <c r="AZ2" s="101"/>
-      <c r="BA2" s="101"/>
-      <c r="BB2" s="101"/>
-      <c r="BC2" s="101"/>
-      <c r="BD2" s="101"/>
-      <c r="BE2" s="101"/>
-      <c r="BF2" s="101"/>
-      <c r="BG2" s="101"/>
-      <c r="BH2" s="101"/>
-      <c r="BI2" s="101"/>
-      <c r="BJ2" s="101"/>
-      <c r="BK2" s="101"/>
-      <c r="BL2" s="101"/>
-      <c r="BM2" s="101"/>
-      <c r="BN2" s="101"/>
-      <c r="BO2" s="101"/>
-      <c r="BP2" s="101"/>
-      <c r="BQ2" s="101"/>
-      <c r="BR2" s="101"/>
-      <c r="BS2" s="101"/>
-      <c r="BT2" s="101"/>
-      <c r="BU2" s="101"/>
-      <c r="BV2" s="101"/>
+      <c r="AW2" s="88"/>
+      <c r="AX2" s="88"/>
+      <c r="AY2" s="88"/>
+      <c r="AZ2" s="88"/>
+      <c r="BA2" s="88"/>
+      <c r="BB2" s="88"/>
+      <c r="BC2" s="88"/>
+      <c r="BD2" s="88"/>
+      <c r="BE2" s="88"/>
+      <c r="BF2" s="88"/>
+      <c r="BG2" s="88"/>
+      <c r="BH2" s="88"/>
+      <c r="BI2" s="88"/>
+      <c r="BJ2" s="88"/>
+      <c r="BK2" s="88"/>
+      <c r="BL2" s="88"/>
+      <c r="BM2" s="88"/>
+      <c r="BN2" s="88"/>
+      <c r="BO2" s="88"/>
+      <c r="BP2" s="88"/>
+      <c r="BQ2" s="88"/>
+      <c r="BR2" s="88"/>
+      <c r="BS2" s="88"/>
+      <c r="BT2" s="88"/>
+      <c r="BU2" s="88"/>
+      <c r="BV2" s="88"/>
     </row>
     <row r="3" spans="2:74" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="104"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="91"/>
       <c r="E3" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="105" t="s">
+      <c r="H3" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="106"/>
-      <c r="J3" s="107"/>
-      <c r="L3" s="111" t="s">
+      <c r="I3" s="93"/>
+      <c r="J3" s="94"/>
+      <c r="L3" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="112"/>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="113"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="100"/>
     </row>
     <row r="4" spans="2:74" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
@@ -1669,87 +1441,87 @@
         <v>3800</v>
       </c>
       <c r="K4" s="15"/>
-      <c r="L4" s="114" t="s">
+      <c r="L4" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="115"/>
-      <c r="N4" s="115"/>
-      <c r="O4" s="115"/>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="116"/>
-      <c r="S4" s="95" t="s">
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="103"/>
+      <c r="S4" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="96"/>
-      <c r="U4" s="96"/>
-      <c r="V4" s="96"/>
-      <c r="W4" s="96"/>
-      <c r="X4" s="97"/>
-      <c r="Z4" s="95" t="s">
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="84"/>
+      <c r="Z4" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="96"/>
-      <c r="AC4" s="96"/>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="97"/>
-      <c r="AH4" s="95" t="s">
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="84"/>
+      <c r="AH4" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="AI4" s="96"/>
-      <c r="AJ4" s="96"/>
-      <c r="AK4" s="96"/>
-      <c r="AL4" s="96"/>
-      <c r="AM4" s="97"/>
-      <c r="AO4" s="95" t="s">
+      <c r="AI4" s="83"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="83"/>
+      <c r="AL4" s="83"/>
+      <c r="AM4" s="84"/>
+      <c r="AO4" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="AP4" s="96"/>
-      <c r="AQ4" s="96"/>
-      <c r="AR4" s="96"/>
-      <c r="AS4" s="96"/>
-      <c r="AT4" s="97"/>
-      <c r="AV4" s="95" t="s">
+      <c r="AP4" s="83"/>
+      <c r="AQ4" s="83"/>
+      <c r="AR4" s="83"/>
+      <c r="AS4" s="83"/>
+      <c r="AT4" s="84"/>
+      <c r="AV4" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="AW4" s="96"/>
-      <c r="AX4" s="96"/>
-      <c r="AY4" s="96"/>
-      <c r="AZ4" s="96"/>
-      <c r="BA4" s="97"/>
+      <c r="AW4" s="83"/>
+      <c r="AX4" s="83"/>
+      <c r="AY4" s="83"/>
+      <c r="AZ4" s="83"/>
+      <c r="BA4" s="84"/>
       <c r="BB4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="BC4" s="95" t="s">
+      <c r="BC4" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="BD4" s="96"/>
-      <c r="BE4" s="96"/>
-      <c r="BF4" s="96"/>
-      <c r="BG4" s="96"/>
-      <c r="BH4" s="97"/>
+      <c r="BD4" s="83"/>
+      <c r="BE4" s="83"/>
+      <c r="BF4" s="83"/>
+      <c r="BG4" s="83"/>
+      <c r="BH4" s="84"/>
       <c r="BI4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="BJ4" s="95" t="s">
+      <c r="BJ4" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="BK4" s="96"/>
-      <c r="BL4" s="96"/>
-      <c r="BM4" s="96"/>
-      <c r="BN4" s="96"/>
-      <c r="BO4" s="97"/>
+      <c r="BK4" s="83"/>
+      <c r="BL4" s="83"/>
+      <c r="BM4" s="83"/>
+      <c r="BN4" s="83"/>
+      <c r="BO4" s="84"/>
       <c r="BP4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="BQ4" s="95" t="s">
+      <c r="BQ4" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="BR4" s="96"/>
-      <c r="BS4" s="96"/>
-      <c r="BT4" s="96"/>
-      <c r="BU4" s="96"/>
-      <c r="BV4" s="97"/>
+      <c r="BR4" s="83"/>
+      <c r="BS4" s="83"/>
+      <c r="BT4" s="83"/>
+      <c r="BU4" s="83"/>
+      <c r="BV4" s="84"/>
     </row>
     <row r="5" spans="2:74" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
@@ -2708,30 +2480,30 @@
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="AH13" s="95" t="s">
+      <c r="AH13" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="AI13" s="96"/>
-      <c r="AJ13" s="96"/>
-      <c r="AK13" s="96"/>
-      <c r="AL13" s="96"/>
-      <c r="AM13" s="97"/>
-      <c r="AO13" s="95" t="s">
+      <c r="AI13" s="83"/>
+      <c r="AJ13" s="83"/>
+      <c r="AK13" s="83"/>
+      <c r="AL13" s="83"/>
+      <c r="AM13" s="84"/>
+      <c r="AO13" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="AP13" s="96"/>
-      <c r="AQ13" s="96"/>
-      <c r="AR13" s="96"/>
-      <c r="AS13" s="96"/>
-      <c r="AT13" s="97"/>
-      <c r="BQ13" s="95" t="s">
+      <c r="AP13" s="83"/>
+      <c r="AQ13" s="83"/>
+      <c r="AR13" s="83"/>
+      <c r="AS13" s="83"/>
+      <c r="AT13" s="84"/>
+      <c r="BQ13" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="BR13" s="96"/>
-      <c r="BS13" s="96"/>
-      <c r="BT13" s="96"/>
-      <c r="BU13" s="96"/>
-      <c r="BV13" s="97"/>
+      <c r="BR13" s="83"/>
+      <c r="BS13" s="83"/>
+      <c r="BT13" s="83"/>
+      <c r="BU13" s="83"/>
+      <c r="BV13" s="84"/>
     </row>
     <row r="14" spans="2:74" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
@@ -2817,11 +2589,11 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="H15" s="108" t="s">
+      <c r="H15" s="95" t="s">
         <v>12</v>
       </c>
-      <c r="I15" s="109"/>
-      <c r="J15" s="110"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="97"/>
       <c r="K15" s="34"/>
       <c r="L15" s="72" t="s">
         <v>84</v>
@@ -3162,11 +2934,11 @@
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
       <c r="F20" s="61"/>
-      <c r="H20" s="108" t="s">
+      <c r="H20" s="95" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="109"/>
-      <c r="J20" s="110"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="97"/>
       <c r="K20" s="19"/>
       <c r="L20" s="69"/>
       <c r="M20" s="68"/>
@@ -3260,30 +3032,30 @@
         <v>5000</v>
       </c>
       <c r="Q22" s="63"/>
-      <c r="AH22" s="95" t="s">
+      <c r="AH22" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="AI22" s="96"/>
-      <c r="AJ22" s="96"/>
-      <c r="AK22" s="96"/>
-      <c r="AL22" s="96"/>
-      <c r="AM22" s="97"/>
-      <c r="AO22" s="95" t="s">
+      <c r="AI22" s="83"/>
+      <c r="AJ22" s="83"/>
+      <c r="AK22" s="83"/>
+      <c r="AL22" s="83"/>
+      <c r="AM22" s="84"/>
+      <c r="AO22" s="82" t="s">
         <v>55</v>
       </c>
-      <c r="AP22" s="96"/>
-      <c r="AQ22" s="96"/>
-      <c r="AR22" s="96"/>
-      <c r="AS22" s="96"/>
-      <c r="AT22" s="97"/>
-      <c r="BQ22" s="95" t="s">
+      <c r="AP22" s="83"/>
+      <c r="AQ22" s="83"/>
+      <c r="AR22" s="83"/>
+      <c r="AS22" s="83"/>
+      <c r="AT22" s="84"/>
+      <c r="BQ22" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="BR22" s="96"/>
-      <c r="BS22" s="96"/>
-      <c r="BT22" s="96"/>
-      <c r="BU22" s="96"/>
-      <c r="BV22" s="97"/>
+      <c r="BR22" s="83"/>
+      <c r="BS22" s="83"/>
+      <c r="BT22" s="83"/>
+      <c r="BU22" s="83"/>
+      <c r="BV22" s="84"/>
     </row>
     <row r="23" spans="2:74" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
@@ -3325,14 +3097,14 @@
       <c r="AT23" s="23">
         <v>209</v>
       </c>
-      <c r="BQ23" s="95" t="s">
+      <c r="BQ23" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="BR23" s="96"/>
-      <c r="BS23" s="96"/>
-      <c r="BT23" s="96"/>
-      <c r="BU23" s="96"/>
-      <c r="BV23" s="97"/>
+      <c r="BR23" s="83"/>
+      <c r="BS23" s="83"/>
+      <c r="BT23" s="83"/>
+      <c r="BU23" s="83"/>
+      <c r="BV23" s="84"/>
     </row>
     <row r="24" spans="2:74" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B24" s="59"/>
@@ -3715,14 +3487,14 @@
       <c r="H32" s="40"/>
       <c r="I32" s="41"/>
       <c r="J32" s="42"/>
-      <c r="BQ32" s="95" t="s">
+      <c r="BQ32" s="82" t="s">
         <v>82</v>
       </c>
-      <c r="BR32" s="96"/>
-      <c r="BS32" s="96"/>
-      <c r="BT32" s="96"/>
-      <c r="BU32" s="96"/>
-      <c r="BV32" s="97"/>
+      <c r="BR32" s="83"/>
+      <c r="BS32" s="83"/>
+      <c r="BT32" s="83"/>
+      <c r="BU32" s="83"/>
+      <c r="BV32" s="84"/>
     </row>
     <row r="33" spans="2:74" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
@@ -3738,14 +3510,14 @@
         <v>200</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="BQ33" s="95" t="s">
+      <c r="BQ33" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="BR33" s="96"/>
-      <c r="BS33" s="96"/>
-      <c r="BT33" s="96"/>
-      <c r="BU33" s="96"/>
-      <c r="BV33" s="97"/>
+      <c r="BR33" s="83"/>
+      <c r="BS33" s="83"/>
+      <c r="BT33" s="83"/>
+      <c r="BU33" s="83"/>
+      <c r="BV33" s="84"/>
     </row>
     <row r="34" spans="2:74" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
@@ -3870,11 +3642,11 @@
       </c>
     </row>
     <row r="40" spans="2:74" x14ac:dyDescent="0.25">
-      <c r="B40" s="98"/>
-      <c r="C40" s="99"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="99"/>
-      <c r="F40" s="100"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="87"/>
       <c r="BQ40" s="3"/>
       <c r="BR40" s="2"/>
       <c r="BS40" s="2"/>
@@ -3892,14 +3664,14 @@
       <c r="C65" s="10"/>
     </row>
     <row r="96" spans="71:76" x14ac:dyDescent="0.25">
-      <c r="BS96" s="95" t="s">
+      <c r="BS96" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="BT96" s="96"/>
-      <c r="BU96" s="96"/>
-      <c r="BV96" s="96"/>
-      <c r="BW96" s="96"/>
-      <c r="BX96" s="97"/>
+      <c r="BT96" s="83"/>
+      <c r="BU96" s="83"/>
+      <c r="BV96" s="83"/>
+      <c r="BW96" s="83"/>
+      <c r="BX96" s="84"/>
     </row>
     <row r="97" spans="71:76" x14ac:dyDescent="0.25">
       <c r="BS97" s="4" t="s">
@@ -3968,14 +3740,14 @@
       </c>
     </row>
     <row r="103" spans="71:76" x14ac:dyDescent="0.25">
-      <c r="BS103" s="95" t="s">
+      <c r="BS103" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="BT103" s="96"/>
-      <c r="BU103" s="96"/>
-      <c r="BV103" s="96"/>
-      <c r="BW103" s="96"/>
-      <c r="BX103" s="97"/>
+      <c r="BT103" s="83"/>
+      <c r="BU103" s="83"/>
+      <c r="BV103" s="83"/>
+      <c r="BW103" s="83"/>
+      <c r="BX103" s="84"/>
     </row>
     <row r="104" spans="71:76" x14ac:dyDescent="0.25">
       <c r="BS104" s="4" t="s">
@@ -4094,7 +3866,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:F61"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4.140625" style="1" bestFit="1" customWidth="1"/>
@@ -5038,610 +4810,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:AK18"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.42578125" style="1" customWidth="1"/>
-    <col min="13" max="14" width="8.7109375" style="1"/>
-    <col min="15" max="15" width="22.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="8.7109375" style="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.7109375" style="1" customWidth="1"/>
-    <col min="25" max="25" width="4.42578125" style="1" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" style="1"/>
-    <col min="27" max="27" width="22.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.28515625" style="1" customWidth="1"/>
-    <col min="30" max="36" width="8.7109375" style="1"/>
-    <col min="37" max="37" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="8.7109375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:37" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="122" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="124" t="s">
-        <v>107</v>
-      </c>
-      <c r="F3" s="126">
-        <v>1</v>
-      </c>
-      <c r="G3" s="128"/>
-      <c r="H3" s="130" t="s">
-        <v>112</v>
-      </c>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="M3" s="117" t="s">
-        <v>103</v>
-      </c>
-      <c r="N3" s="118"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="118"/>
-      <c r="S3" s="118"/>
-      <c r="T3" s="118"/>
-      <c r="U3" s="118"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="119"/>
-      <c r="Y3" s="117" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z3" s="118"/>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="118"/>
-      <c r="AD3" s="118"/>
-      <c r="AE3" s="118"/>
-      <c r="AF3" s="118"/>
-      <c r="AG3" s="118"/>
-      <c r="AH3" s="118"/>
-      <c r="AI3" s="118"/>
-      <c r="AJ3" s="118"/>
-      <c r="AK3" s="119"/>
-    </row>
-    <row r="4" spans="2:37" ht="21" x14ac:dyDescent="0.35">
-      <c r="B4" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="125" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="125" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="127"/>
-      <c r="H4" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="M4" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="O4" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q4" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="R4" s="82" t="s">
-        <v>101</v>
-      </c>
-      <c r="S4" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="T4" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="U4" s="82" t="s">
-        <v>102</v>
-      </c>
-      <c r="V4" s="82" t="s">
-        <v>90</v>
-      </c>
-      <c r="W4" s="82" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y4" s="82" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="82" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB4" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC4" s="82" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD4" s="82" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE4" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="AF4" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG4" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH4" s="82" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI4" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ4" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="AK4" s="82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="2:37" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="129">
-        <v>50000</v>
-      </c>
-      <c r="H5" s="131">
-        <v>2026</v>
-      </c>
-      <c r="I5" s="131"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="3">
-        <v>46023</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="R5" s="83">
-        <v>5</v>
-      </c>
-      <c r="S5" s="2">
-        <v>10</v>
-      </c>
-      <c r="T5" s="2">
-        <v>100</v>
-      </c>
-      <c r="U5" s="2">
-        <v>100</v>
-      </c>
-      <c r="V5" s="89">
-        <v>100</v>
-      </c>
-      <c r="W5" s="87">
-        <f>V5*U5</f>
-        <v>10000</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>46023</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD5" s="83">
-        <v>5</v>
-      </c>
-      <c r="AE5" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF5" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG5" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH5" s="89">
-        <v>100</v>
-      </c>
-      <c r="AI5" s="89">
-        <f>AG5*AH5</f>
-        <v>10000</v>
-      </c>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="87">
-        <f>AI5</f>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="129">
-        <v>50000</v>
-      </c>
-      <c r="H6" s="84"/>
-      <c r="I6" s="132" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" s="132"/>
-      <c r="K6" s="84"/>
-      <c r="M6" s="2">
-        <v>2</v>
-      </c>
-      <c r="N6" s="3">
-        <v>46024</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="R6" s="84">
-        <v>4</v>
-      </c>
-      <c r="S6" s="2">
-        <v>10</v>
-      </c>
-      <c r="T6" s="2">
-        <v>100</v>
-      </c>
-      <c r="U6" s="2">
-        <v>100</v>
-      </c>
-      <c r="V6" s="89">
-        <v>200</v>
-      </c>
-      <c r="W6" s="87">
-        <f t="shared" ref="W6:W8" si="0">V6*U6</f>
-        <v>20000</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>2</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>46024</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD6" s="84">
-        <v>4</v>
-      </c>
-      <c r="AE6" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF6" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG6" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH6" s="89">
-        <v>200</v>
-      </c>
-      <c r="AI6" s="89">
-        <f t="shared" ref="AI6:AI8" si="1">AG6*AH6</f>
-        <v>20000</v>
-      </c>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="87">
-        <f>AK5+AI6-AJ6</f>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="133">
-        <f>E5</f>
-        <v>50000</v>
-      </c>
-      <c r="M7" s="2">
-        <v>3</v>
-      </c>
-      <c r="N7" s="3">
-        <v>46025</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="R7" s="83">
-        <v>7</v>
-      </c>
-      <c r="S7" s="2">
-        <v>10</v>
-      </c>
-      <c r="T7" s="2">
-        <v>100</v>
-      </c>
-      <c r="U7" s="2">
-        <v>100</v>
-      </c>
-      <c r="V7" s="89">
-        <v>250</v>
-      </c>
-      <c r="W7" s="87">
-        <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>46025</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD7" s="83">
-        <v>7</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG7" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH7" s="89">
-        <v>250</v>
-      </c>
-      <c r="AI7" s="89">
-        <f t="shared" si="1"/>
-        <v>25000</v>
-      </c>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="87">
-        <f t="shared" ref="AK7:AK8" si="2">AK6+AI7-AJ7</f>
-        <v>55000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="M8" s="2">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3">
-        <v>46026</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="R8" s="83">
-        <v>1</v>
-      </c>
-      <c r="S8" s="2">
-        <v>10</v>
-      </c>
-      <c r="T8" s="2">
-        <v>100</v>
-      </c>
-      <c r="U8" s="2">
-        <v>100</v>
-      </c>
-      <c r="V8" s="89">
-        <v>50</v>
-      </c>
-      <c r="W8" s="87">
-        <f t="shared" si="0"/>
-        <v>5000</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>46026</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="83">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>10</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG8" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH8" s="89">
-        <v>50</v>
-      </c>
-      <c r="AI8" s="89">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="87">
-        <f t="shared" si="2"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="9" spans="2:37" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="H9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" s="134">
-        <f>K7</f>
-        <v>50000</v>
-      </c>
-      <c r="M9" s="120" t="s">
-        <v>104</v>
-      </c>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="121"/>
-      <c r="S9" s="121"/>
-      <c r="T9" s="121"/>
-      <c r="U9" s="88">
-        <f t="shared" ref="U9" si="3">SUM(U5:U8)</f>
-        <v>400</v>
-      </c>
-      <c r="V9" s="85"/>
-      <c r="W9" s="86">
-        <f>SUM(W5:W8)</f>
-        <v>60000</v>
-      </c>
-      <c r="Y9" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="Z9" s="91"/>
-      <c r="AA9" s="91"/>
-      <c r="AB9" s="91"/>
-      <c r="AC9" s="91"/>
-      <c r="AD9" s="91"/>
-      <c r="AE9" s="91"/>
-      <c r="AF9" s="91"/>
-      <c r="AG9" s="92">
-        <f>SUM(AG5:AG8)</f>
-        <v>400</v>
-      </c>
-      <c r="AH9" s="91"/>
-      <c r="AI9" s="94"/>
-      <c r="AJ9" s="91"/>
-      <c r="AK9" s="93">
-        <f>AK8</f>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H10" s="132"/>
-      <c r="I10" s="132" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="132"/>
-      <c r="K10" s="132"/>
-    </row>
-    <row r="11" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H13" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H15" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="H16" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="133">
-        <f>F6</f>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H17" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="K17" s="133">
-        <f>K16</f>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="18" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="K18" s="134">
-        <f>K17</f>
-        <v>50000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="Y3:AK3"/>
-    <mergeCell ref="M3:W3"/>
-    <mergeCell ref="M9:T9"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="H5:K5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>